--- a/AT32_Work_Bench/arm_can_tool_WorkBench.xlsx
+++ b/AT32_Work_Bench/arm_can_tool_WorkBench.xlsx
@@ -1031,12 +1031,12 @@
   <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">

--- a/AT32_Work_Bench/arm_can_tool_WorkBench.xlsx
+++ b/AT32_Work_Bench/arm_can_tool_WorkBench.xlsx
@@ -127,7 +127,10 @@
     <t>FTa</t>
   </si>
   <si>
-    <t>I2C3_SCL</t>
+    <t>GPIO_Output</t>
+  </si>
+  <si>
+    <t>SOFT_I2C3_SCL</t>
   </si>
   <si>
     <t>9</t>
@@ -136,7 +139,7 @@
     <t>PC1</t>
   </si>
   <si>
-    <t>I2C3_SDA</t>
+    <t>SOFT_I2C3_SDA</t>
   </si>
   <si>
     <t>10</t>
@@ -145,9 +148,6 @@
     <t>PC2</t>
   </si>
   <si>
-    <t>GPIO_Output</t>
-  </si>
-  <si>
     <t>LED0</t>
   </si>
   <si>
@@ -595,7 +595,7 @@
     <t>PB6</t>
   </si>
   <si>
-    <t>I2C1_SCL</t>
+    <t>SOFT_I2C1_SCL</t>
   </si>
   <si>
     <t>59</t>
@@ -604,7 +604,7 @@
     <t>PB7</t>
   </si>
   <si>
-    <t>I2C1_SDA</t>
+    <t>SOFT_I2C1_SDA</t>
   </si>
   <si>
     <t>61</t>
@@ -1031,12 +1031,12 @@
   <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="6" max="6" width="40" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="1" max="1" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -1226,15 +1226,15 @@
         <v>37</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>14</v>
@@ -1243,18 +1243,18 @@
         <v>36</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>14</v>
@@ -1263,7 +1263,7 @@
         <v>36</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>44</v>
@@ -1343,7 +1343,7 @@
         <v>36</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>54</v>
@@ -1363,7 +1363,7 @@
         <v>36</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>57</v>
@@ -1423,7 +1423,7 @@
         <v>15</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>68</v>
@@ -1443,7 +1443,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>71</v>
@@ -1463,7 +1463,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>74</v>
@@ -1483,7 +1483,7 @@
         <v>36</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>77</v>
@@ -1503,7 +1503,7 @@
         <v>36</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>80</v>
@@ -1523,7 +1523,7 @@
         <v>36</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>83</v>
@@ -1603,7 +1603,7 @@
         <v>36</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>98</v>
@@ -1703,7 +1703,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>116</v>
@@ -1843,7 +1843,7 @@
         <v>15</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>134</v>
@@ -1883,7 +1883,7 @@
         <v>15</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>141</v>
@@ -1943,7 +1943,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>150</v>
@@ -2023,7 +2023,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>163</v>
@@ -2123,7 +2123,7 @@
         <v>15</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>178</v>
@@ -2143,7 +2143,7 @@
         <v>15</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>181</v>
@@ -2223,10 +2223,10 @@
         <v>15</v>
       </c>
       <c r="E60" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2243,10 +2243,10 @@
         <v>15</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:6">
